--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Llama-3.3-70B-Instruct/metrics_default_vs_simple.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Llama-3.3-70B-Instruct/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.1355932203389831</v>
+        <v>0.1260504201680672</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.1971830985915493</v>
+        <v>0.176056338028169</v>
       </c>
       <c r="D2">
-        <v>0.8769230769230769</v>
+        <v>0.8863636363636364</v>
       </c>
       <c r="E2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
